--- a/zoho_remediation_benchmarks.xlsx
+++ b/zoho_remediation_benchmarks.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,31 +26,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B91C1C"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000F172A"/>
-      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00B45309"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -65,8 +68,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
         <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,32 +113,32 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,17 +505,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -545,15 +560,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Zoho CRM</t>
+          <t>Zoho CRM - Sales Origination</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Stale Deals (&gt;60 days inactive)</t>
+          <t>Blank / Unattributed Lead Source Inflow</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -563,7 +578,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Deploy Deal Aging Workflow with automated notification alerts to deal owners and auto-stage escalation to Dormant Review queue</t>
+          <t>Deploy UTM parameter capture &amp; mandatory Lead Source validation rules across all webforms, landing pages, and APIs with automated Channel Tagging</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -573,437 +588,521 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Restores pipeline velocity and eliminates revenue leakage</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+          <t>Delivers 100% marketing ROI visibility to leadership and reveals highest converting prospect channels</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marketing Ops / CRM Admin</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Settings &gt; Customization &gt; Modules and Fields &gt; Leads &gt; Validation Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Zoho CRM - Sales Scaling</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Speed-to-Lead Response Lag / Uncontacted Inbound Leads</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Configure 30-minute uncontacted lead alert to Sales Head with automated round-robin re-assignment after 2 hours</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>1-2 Days</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Increases prospect-to-opportunity conversion by over 300% by enforcing sub-15-minute outreach</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Sales Operations Lead</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Settings &gt; Automation &gt; Workflow Rules &gt; Criteria: Lead Status is None / Uncontacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Zoho CRM - Sales Scaling</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Inactive / Missing Lead Assignment Rules</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Configure criteria-based round-robin territory assignment rules with instant mobile push &amp; WhatsApp alerts</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>1-2 Days</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Eliminates admin bottleneck and ensures zero lead leakage at point of origination</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Sales Operations Lead</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Settings &gt; Automation &gt; Lead Assignment Rules &gt; Round Robin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Zoho CRM - Sales Scaling</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Stale Deals &amp; Revenue Stagnation (&gt;60 days inactive)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Deploy Deal Aging Workflow with automated alerts to deal owners and auto-escalation to Dormant Review queue</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>1-2 Days</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Unlocks stalled pipeline value and prevents deals from dying silently</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Zoho Administrator</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Settings &gt; Automation &gt; Workflow Rules &gt; Criteria: Modified Time &gt; 60</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Zoho CRM</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Untouched Leads / Missing Lead Status</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Zoho CRM - Sales Scaling</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Slipped Deals &amp; Expired Closing Date Blindspots</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Deploy automated Closing Date Slippage alert workflow triggering mandatory justification notes when close date passes</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>1-2 Days</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Eliminates phantom pipeline and restores forecasting predictability for leadership</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CRM Configurator</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Settings &gt; Automation &gt; Workflow Rules &gt; Criteria: Closing Date &lt; Today and Stage not Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Zoho CRM - Sales Scaling</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Pipeline Stage Stagnation / Missing Exit Criteria</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Implement Zoho CRM Blueprint state machine with mandatory discovery notes, quote attachments, and stage gates</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>1-2 Weeks</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Enforces sales process governance, prevents skipped stages, and increases win rate</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Lead Systems Architect</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Settings &gt; Automation &gt; Blueprint &gt; Deals Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Zoho CRM - Executive Reporting</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Missing Executive Reporting &amp; Forecasting Dashboards</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Enforce mandatory Lead Status on page layouts and configure automatic default status New on record creation</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>4-6 Hours</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Prevents inbound lead drop-off and standardizes qualification tracking</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>CRM Configurator</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Settings &gt; Customization &gt; Modules and Fields &gt; Layout Rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Zoho CRM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Inactive / Missing Lead Assignment Rules</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Standardize Deal Age, Stage Duration, and Loss Reason picklists; construct 4 Executive Dashboards (Funnel Conversion, Slipped Revenue, Rep Velocity, Win/Loss Intelligence)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2-3 Days</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Equips leadership with trustworthy, real-time pipeline forecasting and rep performance metrics</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>BI / CRM Analyst</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Reports &gt; Create Dashboard &gt; Funnel &amp; Cohort Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Zoho CRM - Security &amp; Governance</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Overprivileged Standard User Profiles (Bulk Export/Delete)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Configure round-robin territory assignment rules with instant mobile push notifications and 2-hour SLA re-assignment</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Revoke global Export Data and Delete Records permissions from non-admin sales profiles; restrict to designated Compliance Officer</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>2-4 Hours</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Eliminates enterprise customer database exfiltration risk</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Security Administrator</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Settings &gt; Users and Control &gt; Security Control &gt; Profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Zoho Desk - Service Governance</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Missing SLA Policies for Secondary Departments</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Create departmental SLA contracts with tiered warning alerts at 75% elapsed duration and supervisor escalations</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2-3 Days</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Restores resolution predictability and protects customer satisfaction</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Support Operations Lead</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Desk Setup &gt; General &gt; SLA &amp; Escalation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Zoho Desk - Service Governance</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Unassigned Ticket Queue Accumulation</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Configure criteria-based skill and round-robin routing rules mapped directly to agent availability schedules</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>1-2 Days</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Eliminates single-admin bottleneck and guarantees 15-minute lead response</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Sales Operations Lead</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Settings &gt; Automation &gt; Lead Assignment Rules &gt; Round Robin</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Zoho CRM</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Overprivileged Standard User Profiles (Bulk Export/Delete)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Eliminates ticket stagnation and reduces first-response time by 45%</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Zoho Desk Administrator</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Desk Setup &gt; Automation &gt; Assignment Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Zoho Books - Financial Operations</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Unsynchronized Customers &amp; Missing Tax IDs (GSTIN)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Revoke global Export Data and Delete Records permissions from non-admin sales profiles; restrict to designated Compliance Officer</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>2-4 Hours</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Eliminates enterprise customer database exfiltration risk</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Security Administrator</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Settings &gt; Users and Control &gt; Security Control &gt; Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Zoho CRM</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline Stage Stagnation / Missing Exit Criteria</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Implement bidirectional CRM Accounts to Books Customers sync with field validation and mandatory Tax ID checks</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>1-2 Weeks</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Guarantees tax compliance and eliminates invoice creation errors</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Deluge Developer</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Zoho Flow / Custom Deluge Function with GSTIN validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Zoho Books - Financial Operations</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Overdue Receivables &amp; Manual Payment Follow-up</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Implement Zoho CRM Blueprint state machine with mandatory checklist fields and transition approval triggers</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>1-2 Weeks</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Enforces sales process governance and accurate forecasting probabilities</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Lead Systems Architect</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Settings &gt; Automation &gt; Blueprint &gt; Deals Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Zoho Desk</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Missing SLA Policies for Secondary Departments</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Activate automated multi-tier payment reminders at +3, +7, and +14 days with embedded direct payment gateway links</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>1 Day</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Accelerates accounts receivable collections and improves operating cashflow</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Finance Lead</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Books Settings &gt; Reminders &gt; Automated Payment Reminders</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Cross-App Sync - Revenue Automation</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Closed-Won Deal to Books Invoice &amp; Customer Onboarding Handoff</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Create departmental SLA contracts with tiered warning alerts at 75% elapsed duration and supervisor escalations</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>2-3 Days</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Restores resolution predictability and protects customer satisfaction</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Support Operations Lead</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Desk Setup &gt; General &gt; SLA &amp; Escalation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Zoho Desk</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Unassigned Ticket Queue Accumulation</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Configure criteria-based skill and round-robin routing rules mapped directly to agent availability schedules</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>1-2 Days</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Eliminates ticket stagnation and reduces first-response time by 45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Zoho Desk Administrator</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Desk Setup &gt; Automation &gt; Assignment Rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Zoho Books</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Unsynchronized Customers &amp; Missing Tax IDs (GSTIN)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Implement bidirectional CRM Accounts to Books Customers sync with field validation and mandatory Tax ID checks</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>1-2 Weeks</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Guarantees tax compliance and eliminates invoice creation errors</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Deluge Developer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Zoho Flow / Custom Deluge Function with GSTIN validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Zoho Books</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Overdue Receivables &amp; Manual Payment Follow-up</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Activate automated multi-tier payment reminders at +3, +7, and +14 days with embedded direct payment gateway links</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>1 Day</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Accelerates accounts receivable collections and improves operating cashflow</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Finance Lead</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Books Settings &gt; Reminders &gt; Automated Payment Reminders</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Cross-App Sync</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Desk Support Escalations Invisible Inside CRM Deals</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Embed Zoho Desk support health telemetry and active escalation widgets directly into CRM Deal and Account views</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>2-3 Days</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Equips account executives with real-time customer health visibility during renewals</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Zoho Suite Consultant</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Zoho CRM Marketplace &gt; Zoho Desk Extension configuration</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Cross-App Sync</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Deal-to-Invoice Webhook Conversion Silent Failures</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Deploy automated retry logic with exponential backoff and error logging queue for failed webhook payload transactions</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Configure automated Deluge trigger on Deal Closed-Won to generate draft invoice in Books and launch customer success project in Desk</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>3-5 Days</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Prevents lost billing transactions and duplicate invoice creation</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Deluge Developer</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>CRM Custom Function with try-catch fallback and audit log module</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Eliminates manual re-entry errors, speeds up invoicing by 100%, and accelerates client time-to-value</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Integration Architect</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Settings &gt; Developer Space &gt; Functions &gt; Deluge Script</t>
         </is>
       </c>
     </row>
